--- a/別紙/別紙E4_ハードウェア管理.xlsx
+++ b/別紙/別紙E4_ハードウェア管理.xlsx
@@ -75,7 +75,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8FBFE"/>
         <bgColor rgb="FFF8FBFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4E1"/>
+        <bgColor rgb="00FFE4E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +156,12 @@
     </xf>
     <xf numFmtId="55" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -690,49 +702,53 @@
       <c r="AD4" s="2" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>C02D53MUML85</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">MacBook Pro (13-inch, 2020, Four Thunderbolt 3 ports) </t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>macOS 15</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Wai Yan Aung</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>使用中</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="n">
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>返却予定</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="n">
         <v>44060</v>
       </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】 データ消去後に返却</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
@@ -1363,39 +1379,43 @@
       <c r="AD16" s="2" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>C02D53MUML85</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">MacBook Pro (13-inch, 2020, Four Thunderbolt 3 ports) </t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>macOS 15</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Wai Yan Aung</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="17" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】 返却予定</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
